--- a/output/Tables/Best practice/Residence/HIA_area_2019_1000replicate_RES.xlsx
+++ b/output/Tables/Best practice/Residence/HIA_area_2019_1000replicate_RES.xlsx
@@ -438,22 +438,22 @@
         </is>
       </c>
       <c r="C2">
-        <v>11286.52</v>
+        <v>11282.471</v>
       </c>
       <c r="D2">
-        <v>9725.612999999999</v>
+        <v>9725.145</v>
       </c>
       <c r="E2">
-        <v>12849.344</v>
+        <v>12844.524</v>
       </c>
       <c r="F2">
-        <v>93685.499</v>
+        <v>93654.363</v>
       </c>
       <c r="G2">
-        <v>84888.068</v>
+        <v>84883.38099999999</v>
       </c>
       <c r="H2">
-        <v>102501.576</v>
+        <v>102472.09</v>
       </c>
       <c r="I2">
         <v>0</v>
@@ -465,13 +465,13 @@
         <v>0</v>
       </c>
       <c r="L2">
-        <v>12460370574.45</v>
+        <v>12455838860.271</v>
       </c>
       <c r="M2">
-        <v>11287460296.992</v>
+        <v>11285444284.297</v>
       </c>
       <c r="N2">
-        <v>13633311768.892</v>
+        <v>13628236366.433</v>
       </c>
     </row>
     <row r="3">
@@ -486,22 +486,22 @@
         </is>
       </c>
       <c r="C3">
-        <v>7788.97</v>
+        <v>7786.727</v>
       </c>
       <c r="D3">
-        <v>6609.346</v>
+        <v>6606.472</v>
       </c>
       <c r="E3">
-        <v>8966.222</v>
+        <v>8960.610000000001</v>
       </c>
       <c r="F3">
-        <v>71586.804</v>
+        <v>71550.726</v>
       </c>
       <c r="G3">
-        <v>64316.337</v>
+        <v>64289.179</v>
       </c>
       <c r="H3">
-        <v>78864.44500000001</v>
+        <v>78824.99800000001</v>
       </c>
       <c r="I3">
         <v>0</v>
@@ -513,13 +513,13 @@
         <v>0</v>
       </c>
       <c r="L3">
-        <v>9519237580.382</v>
+        <v>9514541541.414</v>
       </c>
       <c r="M3">
-        <v>8550350922.807</v>
+        <v>8545349783.294</v>
       </c>
       <c r="N3">
-        <v>10494861403.583</v>
+        <v>10490120471.205</v>
       </c>
     </row>
     <row r="4">
@@ -534,22 +534,22 @@
         </is>
       </c>
       <c r="C4">
-        <v>18020.457</v>
+        <v>18012.358</v>
       </c>
       <c r="D4">
-        <v>16285.733</v>
+        <v>16281.434</v>
       </c>
       <c r="E4">
-        <v>19746.72</v>
+        <v>19736.257</v>
       </c>
       <c r="F4">
-        <v>176584.632</v>
+        <v>176498.858</v>
       </c>
       <c r="G4">
-        <v>165505.08</v>
+        <v>165466.458</v>
       </c>
       <c r="H4">
-        <v>187633.729</v>
+        <v>187552.562</v>
       </c>
       <c r="I4">
         <v>0</v>
@@ -561,13 +561,13 @@
         <v>0</v>
       </c>
       <c r="L4">
-        <v>23491090112.761</v>
+        <v>23479226759.202</v>
       </c>
       <c r="M4">
-        <v>22016466637.008</v>
+        <v>22002701330.646</v>
       </c>
       <c r="N4">
-        <v>24975195466.295</v>
+        <v>24961639631.365</v>
       </c>
     </row>
     <row r="5">
@@ -582,40 +582,40 @@
         </is>
       </c>
       <c r="C5">
-        <v>7888.176</v>
+        <v>7893.74</v>
       </c>
       <c r="D5">
-        <v>6958.01</v>
+        <v>6960.259</v>
       </c>
       <c r="E5">
-        <v>8835.951999999999</v>
+        <v>8842.833000000001</v>
       </c>
       <c r="F5">
-        <v>6267.848</v>
+        <v>6268.987</v>
       </c>
       <c r="G5">
-        <v>5563.393</v>
+        <v>5562.097</v>
       </c>
       <c r="H5">
-        <v>6984.436</v>
+        <v>6984.984</v>
       </c>
       <c r="I5">
-        <v>439503988.949</v>
+        <v>439721863.863</v>
       </c>
       <c r="J5">
-        <v>387342939.199</v>
+        <v>387521354.063</v>
       </c>
       <c r="K5">
-        <v>492198106.321</v>
+        <v>492479073.916</v>
       </c>
       <c r="L5">
-        <v>833670185.266</v>
+        <v>833761698.534</v>
       </c>
       <c r="M5">
-        <v>739691974.903</v>
+        <v>739841089.6339999</v>
       </c>
       <c r="N5">
-        <v>928769481.4</v>
+        <v>929239095.4349999</v>
       </c>
     </row>
     <row r="6">
@@ -630,40 +630,40 @@
         </is>
       </c>
       <c r="C6">
-        <v>5596.924</v>
+        <v>5597.743</v>
       </c>
       <c r="D6">
-        <v>4857.899</v>
+        <v>4857.881</v>
       </c>
       <c r="E6">
-        <v>6347.73</v>
+        <v>6350.12</v>
       </c>
       <c r="F6">
-        <v>4727.125</v>
+        <v>4727.858</v>
       </c>
       <c r="G6">
-        <v>4144.391</v>
+        <v>4144.785</v>
       </c>
       <c r="H6">
-        <v>5320.033</v>
+        <v>5323.924</v>
       </c>
       <c r="I6">
-        <v>311828473.25</v>
+        <v>311932070.336</v>
       </c>
       <c r="J6">
-        <v>270663893.294</v>
+        <v>270660068.888</v>
       </c>
       <c r="K6">
-        <v>353773929.041</v>
+        <v>353951008.053</v>
       </c>
       <c r="L6">
-        <v>628900409.222</v>
+        <v>628932045.75</v>
       </c>
       <c r="M6">
-        <v>551565735.3279999</v>
+        <v>551239664.223</v>
       </c>
       <c r="N6">
-        <v>708072065.705</v>
+        <v>708070973.61</v>
       </c>
     </row>
     <row r="7">
@@ -678,40 +678,40 @@
         </is>
       </c>
       <c r="C7">
-        <v>12881.166</v>
+        <v>12887.699</v>
       </c>
       <c r="D7">
-        <v>11812.12</v>
+        <v>11821.261</v>
       </c>
       <c r="E7">
-        <v>13960.914</v>
+        <v>13967.392</v>
       </c>
       <c r="F7">
-        <v>11128.268</v>
+        <v>11137.108</v>
       </c>
       <c r="G7">
-        <v>10282.455</v>
+        <v>10293.503</v>
       </c>
       <c r="H7">
-        <v>11986.328</v>
+        <v>11990.931</v>
       </c>
       <c r="I7">
-        <v>717660229.526</v>
+        <v>717960329.135</v>
       </c>
       <c r="J7">
-        <v>657792370.33</v>
+        <v>658162607.252</v>
       </c>
       <c r="K7">
-        <v>777826292.226</v>
+        <v>778145756.687</v>
       </c>
       <c r="L7">
-        <v>1480138819.286</v>
+        <v>1481310686.83</v>
       </c>
       <c r="M7">
-        <v>1367862365.394</v>
+        <v>1368965081.543</v>
       </c>
       <c r="N7">
-        <v>1594065979.483</v>
+        <v>1594496606.414</v>
       </c>
     </row>
     <row r="8">
@@ -726,40 +726,40 @@
         </is>
       </c>
       <c r="C8">
-        <v>5616.259</v>
+        <v>5614.204</v>
       </c>
       <c r="D8">
-        <v>4911.051</v>
+        <v>4904.676</v>
       </c>
       <c r="E8">
-        <v>6359.068</v>
+        <v>6360.847</v>
       </c>
       <c r="F8">
-        <v>7375.181</v>
+        <v>7379.506</v>
       </c>
       <c r="G8">
-        <v>6234.001</v>
+        <v>6236.291</v>
       </c>
       <c r="H8">
-        <v>8648.450000000001</v>
+        <v>8670.852000000001</v>
       </c>
       <c r="I8">
-        <v>83137070.07600001</v>
+        <v>83100799.23</v>
       </c>
       <c r="J8">
-        <v>72700470.96799999</v>
+        <v>72659228.851</v>
       </c>
       <c r="K8">
-        <v>94154099.097</v>
+        <v>94203953.76000001</v>
       </c>
       <c r="L8">
-        <v>980731766.803</v>
+        <v>981468846.091</v>
       </c>
       <c r="M8">
-        <v>828740322.3559999</v>
+        <v>829058270.86</v>
       </c>
       <c r="N8">
-        <v>1150015238.373</v>
+        <v>1152887183.452</v>
       </c>
     </row>
     <row r="9">
@@ -774,40 +774,40 @@
         </is>
       </c>
       <c r="C9">
-        <v>4059.127</v>
+        <v>4059.084</v>
       </c>
       <c r="D9">
-        <v>3496.691</v>
+        <v>3495.139</v>
       </c>
       <c r="E9">
-        <v>4657.386</v>
+        <v>4650.762</v>
       </c>
       <c r="F9">
-        <v>5451.604</v>
+        <v>5455.215</v>
       </c>
       <c r="G9">
-        <v>4585.475</v>
+        <v>4589.334</v>
       </c>
       <c r="H9">
-        <v>6391.869</v>
+        <v>6405.538</v>
       </c>
       <c r="I9">
-        <v>60090286.264</v>
+        <v>60079180.933</v>
       </c>
       <c r="J9">
-        <v>51808994.839</v>
+        <v>51758910.648</v>
       </c>
       <c r="K9">
-        <v>68989307.09</v>
+        <v>68905996.07600001</v>
       </c>
       <c r="L9">
-        <v>724787830.836</v>
+        <v>725379136.84</v>
       </c>
       <c r="M9">
-        <v>609901274.266</v>
+        <v>609829586.47</v>
       </c>
       <c r="N9">
-        <v>850779643.827</v>
+        <v>851989108.013</v>
       </c>
     </row>
     <row r="10">
@@ -822,40 +822,40 @@
         </is>
       </c>
       <c r="C10">
-        <v>10420.384</v>
+        <v>10424.672</v>
       </c>
       <c r="D10">
-        <v>9507.221</v>
+        <v>9517.387000000001</v>
       </c>
       <c r="E10">
-        <v>11388.193</v>
+        <v>11380.193</v>
       </c>
       <c r="F10">
-        <v>15762.322</v>
+        <v>15803.277</v>
       </c>
       <c r="G10">
-        <v>14110.502</v>
+        <v>14158.15</v>
       </c>
       <c r="H10">
-        <v>17523.085</v>
+        <v>17561.017</v>
       </c>
       <c r="I10">
-        <v>154289341.759</v>
+        <v>154353763.425</v>
       </c>
       <c r="J10">
-        <v>140738138.371</v>
+        <v>140930485.514</v>
       </c>
       <c r="K10">
-        <v>168723785.515</v>
+        <v>168598069.761</v>
       </c>
       <c r="L10">
-        <v>2095640331.738</v>
+        <v>2101364064.092</v>
       </c>
       <c r="M10">
-        <v>1878089237.927</v>
+        <v>1884292457.152</v>
       </c>
       <c r="N10">
-        <v>2329738751.042</v>
+        <v>2334967736.38</v>
       </c>
     </row>
     <row r="11">
@@ -870,40 +870,40 @@
         </is>
       </c>
       <c r="C11">
-        <v>1113.265</v>
+        <v>1111.76</v>
       </c>
       <c r="D11">
-        <v>966.901</v>
+        <v>966.268</v>
       </c>
       <c r="E11">
-        <v>1266.232</v>
+        <v>1265.765</v>
       </c>
       <c r="F11">
-        <v>1899.466</v>
+        <v>1895.642</v>
       </c>
       <c r="G11">
-        <v>1644.633</v>
+        <v>1642.63</v>
       </c>
       <c r="H11">
-        <v>2170.88</v>
+        <v>2165.404</v>
       </c>
       <c r="I11">
-        <v>83706009.612</v>
+        <v>83627684.941</v>
       </c>
       <c r="J11">
-        <v>72735786.237</v>
+        <v>72628681.156</v>
       </c>
       <c r="K11">
-        <v>95241445.234</v>
+        <v>95174424.686</v>
       </c>
       <c r="L11">
-        <v>252645694.04</v>
+        <v>252164404.539</v>
       </c>
       <c r="M11">
-        <v>218772365.2</v>
+        <v>218501392.166</v>
       </c>
       <c r="N11">
-        <v>288567016.923</v>
+        <v>287894233.549</v>
       </c>
     </row>
     <row r="12">
@@ -918,40 +918,40 @@
         </is>
       </c>
       <c r="C12">
-        <v>844.054</v>
+        <v>845.471</v>
       </c>
       <c r="D12">
-        <v>719.838</v>
+        <v>722.273</v>
       </c>
       <c r="E12">
-        <v>975.2809999999999</v>
+        <v>974.982</v>
       </c>
       <c r="F12">
-        <v>1536.617</v>
+        <v>1537.744</v>
       </c>
       <c r="G12">
-        <v>1302.524</v>
+        <v>1306.425</v>
       </c>
       <c r="H12">
-        <v>1785.159</v>
+        <v>1784.862</v>
       </c>
       <c r="I12">
-        <v>63488473.236</v>
+        <v>63587226.778</v>
       </c>
       <c r="J12">
-        <v>54167626.853</v>
+        <v>54376055.513</v>
       </c>
       <c r="K12">
-        <v>73408948.715</v>
+        <v>73289470.994</v>
       </c>
       <c r="L12">
-        <v>204382472.895</v>
+        <v>204518582.911</v>
       </c>
       <c r="M12">
-        <v>173333366.792</v>
+        <v>173752244.712</v>
       </c>
       <c r="N12">
-        <v>237516501.624</v>
+        <v>237333822.679</v>
       </c>
     </row>
     <row r="13">
@@ -966,40 +966,40 @@
         </is>
       </c>
       <c r="C13">
-        <v>2086.931</v>
+        <v>2087.059</v>
       </c>
       <c r="D13">
-        <v>1896.247</v>
+        <v>1896.548</v>
       </c>
       <c r="E13">
-        <v>2284.813</v>
+        <v>2283.89</v>
       </c>
       <c r="F13">
-        <v>4124.454</v>
+        <v>4122.534</v>
       </c>
       <c r="G13">
-        <v>3734.309</v>
+        <v>3732.184</v>
       </c>
       <c r="H13">
-        <v>4538.274</v>
+        <v>4533.082</v>
       </c>
       <c r="I13">
-        <v>156924101.491</v>
+        <v>156956646.098</v>
       </c>
       <c r="J13">
-        <v>142695839.107</v>
+        <v>142643662.643</v>
       </c>
       <c r="K13">
-        <v>171904538.165</v>
+        <v>171776071.914</v>
       </c>
       <c r="L13">
-        <v>548536458.5549999</v>
+        <v>548169253.039</v>
       </c>
       <c r="M13">
-        <v>496451168.713</v>
+        <v>496050128.631</v>
       </c>
       <c r="N13">
-        <v>603720467.293</v>
+        <v>602966033.369</v>
       </c>
     </row>
     <row r="14">
@@ -1014,40 +1014,40 @@
         </is>
       </c>
       <c r="C14">
-        <v>2896.024</v>
+        <v>2895.646</v>
       </c>
       <c r="D14">
-        <v>2466.001</v>
+        <v>2464.83</v>
       </c>
       <c r="E14">
-        <v>3336.072</v>
+        <v>3331.83</v>
       </c>
       <c r="F14">
-        <v>4430.609</v>
+        <v>4436.141</v>
       </c>
       <c r="G14">
-        <v>3822.262</v>
+        <v>3829.93</v>
       </c>
       <c r="H14">
-        <v>5057.899</v>
+        <v>5060.22</v>
       </c>
       <c r="I14">
-        <v>48773679.358</v>
+        <v>48761524.456</v>
       </c>
       <c r="J14">
-        <v>41534093.98</v>
+        <v>41537930.544</v>
       </c>
       <c r="K14">
-        <v>56182943.403</v>
+        <v>56125147.153</v>
       </c>
       <c r="L14">
-        <v>589124638.2539999</v>
+        <v>590025951.4299999</v>
       </c>
       <c r="M14">
-        <v>508013125.603</v>
+        <v>508853593.245</v>
       </c>
       <c r="N14">
-        <v>672306349.313</v>
+        <v>672724291.7180001</v>
       </c>
     </row>
     <row r="15">
@@ -1062,40 +1062,40 @@
         </is>
       </c>
       <c r="C15">
-        <v>2018.711</v>
+        <v>2018.165</v>
       </c>
       <c r="D15">
-        <v>1657.978</v>
+        <v>1658.429</v>
       </c>
       <c r="E15">
-        <v>2391.481</v>
+        <v>2389.422</v>
       </c>
       <c r="F15">
-        <v>3129.755</v>
+        <v>3132.571</v>
       </c>
       <c r="G15">
-        <v>2690.437</v>
+        <v>2693.149</v>
       </c>
       <c r="H15">
-        <v>3579.951</v>
+        <v>3582.609</v>
       </c>
       <c r="I15">
-        <v>33974556.467</v>
+        <v>33973019.473</v>
       </c>
       <c r="J15">
-        <v>27872881.37</v>
+        <v>27897085.234</v>
       </c>
       <c r="K15">
-        <v>40251153.923</v>
+        <v>40192686.859</v>
       </c>
       <c r="L15">
-        <v>416088285.563</v>
+        <v>416491556.891</v>
       </c>
       <c r="M15">
-        <v>357791319.023</v>
+        <v>358329159.424</v>
       </c>
       <c r="N15">
-        <v>476185333.639</v>
+        <v>476607849.154</v>
       </c>
     </row>
     <row r="16">
@@ -1110,40 +1110,40 @@
         </is>
       </c>
       <c r="C16">
-        <v>4693.33</v>
+        <v>4693.013</v>
       </c>
       <c r="D16">
-        <v>4176.187</v>
+        <v>4175.498</v>
       </c>
       <c r="E16">
-        <v>5218.538</v>
+        <v>5217</v>
       </c>
       <c r="F16">
-        <v>7647.463</v>
+        <v>7650.865</v>
       </c>
       <c r="G16">
-        <v>6918.89</v>
+        <v>6923.502</v>
       </c>
       <c r="H16">
-        <v>8392.302</v>
+        <v>8393.128000000001</v>
       </c>
       <c r="I16">
-        <v>79061557.506</v>
+        <v>79022728.59</v>
       </c>
       <c r="J16">
-        <v>70324013.46600001</v>
+        <v>70317892.15700001</v>
       </c>
       <c r="K16">
-        <v>87915040.06900001</v>
+        <v>87878698.911</v>
       </c>
       <c r="L16">
-        <v>1017306469.998</v>
+        <v>1017826974.378</v>
       </c>
       <c r="M16">
-        <v>920206285.625</v>
+        <v>920673598.3559999</v>
       </c>
       <c r="N16">
-        <v>1116307046.021</v>
+        <v>1116328638.231</v>
       </c>
     </row>
     <row r="17">
@@ -1158,22 +1158,22 @@
         </is>
       </c>
       <c r="C17">
-        <v>24539.667</v>
+        <v>20406.012</v>
       </c>
       <c r="D17">
-        <v>21906.097</v>
+        <v>18160.402</v>
       </c>
       <c r="E17">
-        <v>27230.838</v>
+        <v>22739.956</v>
       </c>
       <c r="F17">
-        <v>62587.321</v>
+        <v>5798.821</v>
       </c>
       <c r="G17">
-        <v>52497.721</v>
+        <v>4871.96</v>
       </c>
       <c r="H17">
-        <v>73497.262</v>
+        <v>6843.454</v>
       </c>
       <c r="I17">
         <v>0</v>
@@ -1185,13 +1185,13 @@
         <v>0</v>
       </c>
       <c r="L17">
-        <v>8326230868.558</v>
+        <v>771241764.448</v>
       </c>
       <c r="M17">
-        <v>6980922949.698</v>
+        <v>648025897.766</v>
       </c>
       <c r="N17">
-        <v>9770497283.392</v>
+        <v>909892711.029</v>
       </c>
     </row>
     <row r="18">
@@ -1206,22 +1206,22 @@
         </is>
       </c>
       <c r="C18">
-        <v>18276.103</v>
+        <v>15202.821</v>
       </c>
       <c r="D18">
-        <v>16271.323</v>
+        <v>13483.852</v>
       </c>
       <c r="E18">
-        <v>20278.154</v>
+        <v>16940.515</v>
       </c>
       <c r="F18">
-        <v>47626.546</v>
+        <v>4433.81</v>
       </c>
       <c r="G18">
-        <v>40811.155</v>
+        <v>3793.325</v>
       </c>
       <c r="H18">
-        <v>54629.671</v>
+        <v>5100.817</v>
       </c>
       <c r="I18">
         <v>0</v>
@@ -1233,13 +1233,13 @@
         <v>0</v>
       </c>
       <c r="L18">
-        <v>6335538487.606</v>
+        <v>589881141.766</v>
       </c>
       <c r="M18">
-        <v>5432084321.172</v>
+        <v>504695756.451</v>
       </c>
       <c r="N18">
-        <v>7268274495.708</v>
+        <v>678737074.369</v>
       </c>
     </row>
     <row r="19">
@@ -1254,22 +1254,22 @@
         </is>
       </c>
       <c r="C19">
-        <v>51193.318</v>
+        <v>42430.879</v>
       </c>
       <c r="D19">
-        <v>47685.583</v>
+        <v>39401.727</v>
       </c>
       <c r="E19">
-        <v>54717.365</v>
+        <v>45485.341</v>
       </c>
       <c r="F19">
-        <v>151285.38</v>
+        <v>13891.881</v>
       </c>
       <c r="G19">
-        <v>137495.145</v>
+        <v>12607.072</v>
       </c>
       <c r="H19">
-        <v>165359.028</v>
+        <v>15216.2</v>
       </c>
       <c r="I19">
         <v>0</v>
@@ -1281,13 +1281,13 @@
         <v>0</v>
       </c>
       <c r="L19">
-        <v>20121200669.875</v>
+        <v>1848067351.039</v>
       </c>
       <c r="M19">
-        <v>18303672082.14</v>
+        <v>1678184552.296</v>
       </c>
       <c r="N19">
-        <v>21996540919.044</v>
+        <v>2024141742.989</v>
       </c>
     </row>
     <row r="20">
@@ -1297,40 +1297,40 @@
         </is>
       </c>
       <c r="C20">
-        <v>154123.439</v>
+        <v>138167.968</v>
       </c>
       <c r="D20">
-        <v>139289.147</v>
+        <v>124486.43</v>
       </c>
       <c r="E20">
-        <v>169248.017</v>
+        <v>152180.848</v>
       </c>
       <c r="F20">
-        <v>334979.959</v>
+        <v>97671.95999999999</v>
       </c>
       <c r="G20">
-        <v>295837.2929999999</v>
+        <v>86384.337</v>
       </c>
       <c r="H20">
-        <v>375864.627</v>
+        <v>109617.022</v>
       </c>
       <c r="I20">
-        <v>2232437767.494</v>
+        <v>2233076837.258</v>
       </c>
       <c r="J20">
-        <v>1990377048.014</v>
+        <v>1991093962.463</v>
       </c>
       <c r="K20">
-        <v>2480569588.799</v>
+        <v>2480720358.77</v>
       </c>
       <c r="L20">
-        <v>44554923388.495</v>
+        <v>12990603458.578</v>
       </c>
       <c r="M20">
-        <v>39367097894.14</v>
+        <v>11490292472.929</v>
       </c>
       <c r="N20">
-        <v>49991356572.787</v>
+        <v>14578277100.391</v>
       </c>
     </row>
     <row r="21">
@@ -1340,40 +1340,40 @@
         </is>
       </c>
       <c r="C21">
-        <v>191219.386</v>
+        <v>175249.524</v>
       </c>
       <c r="D21">
-        <v>171909.839</v>
+        <v>157099.481</v>
       </c>
       <c r="E21">
-        <v>210810.303</v>
+        <v>193722.239</v>
       </c>
       <c r="F21">
-        <v>676836.8940000001</v>
+        <v>439375.907</v>
       </c>
       <c r="G21">
-        <v>610546.7779999999</v>
+        <v>401023.355</v>
       </c>
       <c r="H21">
-        <v>744864.3769999999</v>
+        <v>478466.672</v>
       </c>
       <c r="I21">
-        <v>2232437767.494</v>
+        <v>2233076837.258</v>
       </c>
       <c r="J21">
-        <v>1990377048.014</v>
+        <v>1991093962.463</v>
       </c>
       <c r="K21">
-        <v>2480569588.799</v>
+        <v>2480720358.77</v>
       </c>
       <c r="L21">
-        <v>90025621656.088</v>
+        <v>58440210619.465</v>
       </c>
       <c r="M21">
-        <v>81221375750.94699</v>
+        <v>53323787871.166</v>
       </c>
       <c r="N21">
-        <v>99094725211.55701</v>
+        <v>63658273569.39402</v>
       </c>
     </row>
   </sheetData>

--- a/output/Tables/Best practice/Residence/HIA_area_2019_1000replicate_RES.xlsx
+++ b/output/Tables/Best practice/Residence/HIA_area_2019_1000replicate_RES.xlsx
@@ -438,22 +438,22 @@
         </is>
       </c>
       <c r="C2">
-        <v>11282.471</v>
+        <v>17297.015</v>
       </c>
       <c r="D2">
-        <v>9725.145</v>
+        <v>15546.688</v>
       </c>
       <c r="E2">
-        <v>12844.524</v>
+        <v>19051.461</v>
       </c>
       <c r="F2">
-        <v>93654.363</v>
+        <v>156123.485</v>
       </c>
       <c r="G2">
-        <v>84883.38099999999</v>
+        <v>145839.976</v>
       </c>
       <c r="H2">
-        <v>102472.09</v>
+        <v>166468.978</v>
       </c>
       <c r="I2">
         <v>0</v>
@@ -465,13 +465,13 @@
         <v>0</v>
       </c>
       <c r="L2">
-        <v>12455838860.271</v>
+        <v>20765612100.156</v>
       </c>
       <c r="M2">
-        <v>11285444284.297</v>
+        <v>19391149302.275</v>
       </c>
       <c r="N2">
-        <v>13628236366.433</v>
+        <v>22139529088.148</v>
       </c>
     </row>
     <row r="3">
@@ -486,22 +486,22 @@
         </is>
       </c>
       <c r="C3">
-        <v>7786.727</v>
+        <v>14421.137</v>
       </c>
       <c r="D3">
-        <v>6606.472</v>
+        <v>13027.762</v>
       </c>
       <c r="E3">
-        <v>8960.610000000001</v>
+        <v>15809.741</v>
       </c>
       <c r="F3">
-        <v>71550.726</v>
+        <v>150023.904</v>
       </c>
       <c r="G3">
-        <v>64289.179</v>
+        <v>140191.306</v>
       </c>
       <c r="H3">
-        <v>78824.99800000001</v>
+        <v>159888.716</v>
       </c>
       <c r="I3">
         <v>0</v>
@@ -513,13 +513,13 @@
         <v>0</v>
       </c>
       <c r="L3">
-        <v>9514541541.414</v>
+        <v>19950665546.293</v>
       </c>
       <c r="M3">
-        <v>8545349783.294</v>
+        <v>18638561066.204</v>
       </c>
       <c r="N3">
-        <v>10490120471.205</v>
+        <v>21275044775.269</v>
       </c>
     </row>
     <row r="4">
@@ -534,22 +534,22 @@
         </is>
       </c>
       <c r="C4">
-        <v>18012.358</v>
+        <v>26774.77</v>
       </c>
       <c r="D4">
-        <v>16281.434</v>
+        <v>24775.445</v>
       </c>
       <c r="E4">
-        <v>19736.257</v>
+        <v>28763.489</v>
       </c>
       <c r="F4">
-        <v>176498.858</v>
+        <v>298583.004</v>
       </c>
       <c r="G4">
-        <v>165466.458</v>
+        <v>284898.496</v>
       </c>
       <c r="H4">
-        <v>187552.562</v>
+        <v>312266.269</v>
       </c>
       <c r="I4">
         <v>0</v>
@@ -561,13 +561,13 @@
         <v>0</v>
       </c>
       <c r="L4">
-        <v>23479226759.202</v>
+        <v>39717138240.38</v>
       </c>
       <c r="M4">
-        <v>22002701330.646</v>
+        <v>37892182879.655</v>
       </c>
       <c r="N4">
-        <v>24961639631.365</v>
+        <v>41553182267.878</v>
       </c>
     </row>
     <row r="5">
@@ -582,40 +582,40 @@
         </is>
       </c>
       <c r="C5">
-        <v>7893.74</v>
+        <v>11472.925</v>
       </c>
       <c r="D5">
-        <v>6960.259</v>
+        <v>10435.808</v>
       </c>
       <c r="E5">
-        <v>8842.833000000001</v>
+        <v>12524.763</v>
       </c>
       <c r="F5">
-        <v>6268.987</v>
+        <v>9321.355</v>
       </c>
       <c r="G5">
-        <v>5562.097</v>
+        <v>8541.73</v>
       </c>
       <c r="H5">
-        <v>6984.984</v>
+        <v>10112.54</v>
       </c>
       <c r="I5">
-        <v>439721863.863</v>
+        <v>639083997.099</v>
       </c>
       <c r="J5">
-        <v>387521354.063</v>
+        <v>581084801.827</v>
       </c>
       <c r="K5">
-        <v>492479073.916</v>
+        <v>697712548.822</v>
       </c>
       <c r="L5">
-        <v>833761698.534</v>
+        <v>1239723582.979</v>
       </c>
       <c r="M5">
-        <v>739841089.6339999</v>
+        <v>1135789542.261</v>
       </c>
       <c r="N5">
-        <v>929239095.4349999</v>
+        <v>1345159125.143</v>
       </c>
     </row>
     <row r="6">
@@ -630,40 +630,40 @@
         </is>
       </c>
       <c r="C6">
-        <v>5597.743</v>
+        <v>9713.377</v>
       </c>
       <c r="D6">
-        <v>4857.881</v>
+        <v>8827.186</v>
       </c>
       <c r="E6">
-        <v>6350.12</v>
+        <v>10613.922</v>
       </c>
       <c r="F6">
-        <v>4727.858</v>
+        <v>8712.075999999999</v>
       </c>
       <c r="G6">
-        <v>4144.785</v>
+        <v>7948.56</v>
       </c>
       <c r="H6">
-        <v>5323.924</v>
+        <v>9497.772000000001</v>
       </c>
       <c r="I6">
-        <v>311932070.336</v>
+        <v>541206377.4170001</v>
       </c>
       <c r="J6">
-        <v>270660068.888</v>
+        <v>491723496.443</v>
       </c>
       <c r="K6">
-        <v>353951008.053</v>
+        <v>591471577.337</v>
       </c>
       <c r="L6">
-        <v>628932045.75</v>
+        <v>1159009885.987</v>
       </c>
       <c r="M6">
-        <v>551239664.223</v>
+        <v>1057506195.558</v>
       </c>
       <c r="N6">
-        <v>708070973.61</v>
+        <v>1263354825.243</v>
       </c>
     </row>
     <row r="7">
@@ -678,40 +678,40 @@
         </is>
       </c>
       <c r="C7">
-        <v>12887.699</v>
+        <v>18947.677</v>
       </c>
       <c r="D7">
-        <v>11821.261</v>
+        <v>17723.088</v>
       </c>
       <c r="E7">
-        <v>13967.392</v>
+        <v>20182.937</v>
       </c>
       <c r="F7">
-        <v>11137.108</v>
+        <v>17888.351</v>
       </c>
       <c r="G7">
-        <v>10293.503</v>
+        <v>16861.307</v>
       </c>
       <c r="H7">
-        <v>11990.931</v>
+        <v>18927.608</v>
       </c>
       <c r="I7">
-        <v>717960329.135</v>
+        <v>1055517058.74</v>
       </c>
       <c r="J7">
-        <v>658162607.252</v>
+        <v>987045327.9400001</v>
       </c>
       <c r="K7">
-        <v>778145756.687</v>
+        <v>1124508490.134</v>
       </c>
       <c r="L7">
-        <v>1481310686.83</v>
+        <v>2379377282.076</v>
       </c>
       <c r="M7">
-        <v>1368965081.543</v>
+        <v>2242452418.479</v>
       </c>
       <c r="N7">
-        <v>1594496606.414</v>
+        <v>2517129625.951</v>
       </c>
     </row>
     <row r="8">
@@ -726,40 +726,40 @@
         </is>
       </c>
       <c r="C8">
-        <v>5614.204</v>
+        <v>8092.691</v>
       </c>
       <c r="D8">
-        <v>4904.676</v>
+        <v>7286.138</v>
       </c>
       <c r="E8">
-        <v>6360.847</v>
+        <v>8935.870999999999</v>
       </c>
       <c r="F8">
-        <v>7379.506</v>
+        <v>11163.711</v>
       </c>
       <c r="G8">
-        <v>6236.291</v>
+        <v>9772.101000000001</v>
       </c>
       <c r="H8">
-        <v>8670.852000000001</v>
+        <v>12720.468</v>
       </c>
       <c r="I8">
-        <v>83100799.23</v>
+        <v>119799970.005</v>
       </c>
       <c r="J8">
-        <v>72659228.851</v>
+        <v>107881367.136</v>
       </c>
       <c r="K8">
-        <v>94203953.76000001</v>
+        <v>132329000.068</v>
       </c>
       <c r="L8">
-        <v>981468846.091</v>
+        <v>1484571859.938</v>
       </c>
       <c r="M8">
-        <v>829058270.86</v>
+        <v>1299104700.723</v>
       </c>
       <c r="N8">
-        <v>1152887183.452</v>
+        <v>1691703090.908</v>
       </c>
     </row>
     <row r="9">
@@ -774,40 +774,40 @@
         </is>
       </c>
       <c r="C9">
-        <v>4059.084</v>
+        <v>6844.618</v>
       </c>
       <c r="D9">
-        <v>3495.139</v>
+        <v>6181.848</v>
       </c>
       <c r="E9">
-        <v>4650.762</v>
+        <v>7539.55</v>
       </c>
       <c r="F9">
-        <v>5455.215</v>
+        <v>9568.643</v>
       </c>
       <c r="G9">
-        <v>4589.334</v>
+        <v>8494.361000000001</v>
       </c>
       <c r="H9">
-        <v>6405.538</v>
+        <v>10734.445</v>
       </c>
       <c r="I9">
-        <v>60079180.933</v>
+        <v>101309575.762</v>
       </c>
       <c r="J9">
-        <v>51758910.648</v>
+        <v>91513640.325</v>
       </c>
       <c r="K9">
-        <v>68905996.07600001</v>
+        <v>111672984.301</v>
       </c>
       <c r="L9">
-        <v>725379136.84</v>
+        <v>1272156968.585</v>
       </c>
       <c r="M9">
-        <v>609829586.47</v>
+        <v>1130083001.31</v>
       </c>
       <c r="N9">
-        <v>851989108.013</v>
+        <v>1427687095.546</v>
       </c>
     </row>
     <row r="10">
@@ -822,40 +822,40 @@
         </is>
       </c>
       <c r="C10">
-        <v>10424.672</v>
+        <v>16267.713</v>
       </c>
       <c r="D10">
-        <v>9517.387000000001</v>
+        <v>15186.183</v>
       </c>
       <c r="E10">
-        <v>11380.193</v>
+        <v>17394.517</v>
       </c>
       <c r="F10">
-        <v>15803.277</v>
+        <v>26280.255</v>
       </c>
       <c r="G10">
-        <v>14158.15</v>
+        <v>24223.909</v>
       </c>
       <c r="H10">
-        <v>17561.017</v>
+        <v>28451.792</v>
       </c>
       <c r="I10">
-        <v>154353763.425</v>
+        <v>240891229.837</v>
       </c>
       <c r="J10">
-        <v>140930485.514</v>
+        <v>224859849.878</v>
       </c>
       <c r="K10">
-        <v>168598069.761</v>
+        <v>257653995.721</v>
       </c>
       <c r="L10">
-        <v>2101364064.092</v>
+        <v>3494967615.946</v>
       </c>
       <c r="M10">
-        <v>1884292457.152</v>
+        <v>3222948265.595</v>
       </c>
       <c r="N10">
-        <v>2334967736.38</v>
+        <v>3783553944.516</v>
       </c>
     </row>
     <row r="11">
@@ -870,40 +870,40 @@
         </is>
       </c>
       <c r="C11">
-        <v>1111.76</v>
+        <v>1600.047</v>
       </c>
       <c r="D11">
-        <v>966.268</v>
+        <v>1437.474</v>
       </c>
       <c r="E11">
-        <v>1265.765</v>
+        <v>1770.453</v>
       </c>
       <c r="F11">
-        <v>1895.642</v>
+        <v>2861.881</v>
       </c>
       <c r="G11">
-        <v>1642.63</v>
+        <v>2563.253</v>
       </c>
       <c r="H11">
-        <v>2165.404</v>
+        <v>3174.396</v>
       </c>
       <c r="I11">
-        <v>83627684.941</v>
+        <v>120341117.529</v>
       </c>
       <c r="J11">
-        <v>72628681.156</v>
+        <v>108033332.419</v>
       </c>
       <c r="K11">
-        <v>95174424.686</v>
+        <v>133122961.199</v>
       </c>
       <c r="L11">
-        <v>252164404.539</v>
+        <v>380643427.115</v>
       </c>
       <c r="M11">
-        <v>218501392.166</v>
+        <v>340935925.642</v>
       </c>
       <c r="N11">
-        <v>287894233.549</v>
+        <v>422261729.862</v>
       </c>
     </row>
     <row r="12">
@@ -918,40 +918,40 @@
         </is>
       </c>
       <c r="C12">
-        <v>845.471</v>
+        <v>1440.782</v>
       </c>
       <c r="D12">
-        <v>722.273</v>
+        <v>1293.136</v>
       </c>
       <c r="E12">
-        <v>974.982</v>
+        <v>1594.855</v>
       </c>
       <c r="F12">
-        <v>1537.744</v>
+        <v>2647.575</v>
       </c>
       <c r="G12">
-        <v>1306.425</v>
+        <v>2369.506</v>
       </c>
       <c r="H12">
-        <v>1784.862</v>
+        <v>2939.902</v>
       </c>
       <c r="I12">
-        <v>63587226.778</v>
+        <v>108370155.887</v>
       </c>
       <c r="J12">
-        <v>54376055.513</v>
+        <v>97336795.15099999</v>
       </c>
       <c r="K12">
-        <v>73289470.994</v>
+        <v>119918234.013</v>
       </c>
       <c r="L12">
-        <v>204518582.911</v>
+        <v>352030795.456</v>
       </c>
       <c r="M12">
-        <v>173752244.712</v>
+        <v>315312476.419</v>
       </c>
       <c r="N12">
-        <v>237333822.679</v>
+        <v>390860248.244</v>
       </c>
     </row>
     <row r="13">
@@ -966,40 +966,40 @@
         </is>
       </c>
       <c r="C13">
-        <v>2087.059</v>
+        <v>3361.316</v>
       </c>
       <c r="D13">
-        <v>1896.548</v>
+        <v>3132.525</v>
       </c>
       <c r="E13">
-        <v>2283.89</v>
+        <v>3596.252</v>
       </c>
       <c r="F13">
-        <v>4122.534</v>
+        <v>6991.624</v>
       </c>
       <c r="G13">
-        <v>3732.184</v>
+        <v>6501.268</v>
       </c>
       <c r="H13">
-        <v>4533.082</v>
+        <v>7501.719</v>
       </c>
       <c r="I13">
-        <v>156956646.098</v>
+        <v>252797211.378</v>
       </c>
       <c r="J13">
-        <v>142643662.643</v>
+        <v>235549603.588</v>
       </c>
       <c r="K13">
-        <v>171776071.914</v>
+        <v>270469842.189</v>
       </c>
       <c r="L13">
-        <v>548169253.039</v>
+        <v>929753252.064</v>
       </c>
       <c r="M13">
-        <v>496050128.631</v>
+        <v>864354678.102</v>
       </c>
       <c r="N13">
-        <v>602966033.369</v>
+        <v>997489931.5650001</v>
       </c>
     </row>
     <row r="14">
@@ -1014,40 +1014,40 @@
         </is>
       </c>
       <c r="C14">
-        <v>2895.646</v>
+        <v>4169.365</v>
       </c>
       <c r="D14">
-        <v>2464.83</v>
+        <v>3685.52</v>
       </c>
       <c r="E14">
-        <v>3331.83</v>
+        <v>4658.943</v>
       </c>
       <c r="F14">
-        <v>4436.141</v>
+        <v>6387.084</v>
       </c>
       <c r="G14">
-        <v>3829.93</v>
+        <v>5724.156</v>
       </c>
       <c r="H14">
-        <v>5060.22</v>
+        <v>7064.649</v>
       </c>
       <c r="I14">
-        <v>48761524.456</v>
+        <v>70211776.04899999</v>
       </c>
       <c r="J14">
-        <v>41537930.544</v>
+        <v>62094856.609</v>
       </c>
       <c r="K14">
-        <v>56125147.153</v>
+        <v>78461542.69</v>
       </c>
       <c r="L14">
-        <v>590025951.4299999</v>
+        <v>849464958.663</v>
       </c>
       <c r="M14">
-        <v>508853593.245</v>
+        <v>760911541.575</v>
       </c>
       <c r="N14">
-        <v>672724291.7180001</v>
+        <v>939517362.214</v>
       </c>
     </row>
     <row r="15">
@@ -1062,40 +1062,40 @@
         </is>
       </c>
       <c r="C15">
-        <v>2018.165</v>
+        <v>3218.314</v>
       </c>
       <c r="D15">
-        <v>1658.429</v>
+        <v>2811.836</v>
       </c>
       <c r="E15">
-        <v>2389.422</v>
+        <v>3636.602</v>
       </c>
       <c r="F15">
-        <v>3132.571</v>
+        <v>5523.85</v>
       </c>
       <c r="G15">
-        <v>2693.149</v>
+        <v>4988.174</v>
       </c>
       <c r="H15">
-        <v>3582.609</v>
+        <v>6070.321</v>
       </c>
       <c r="I15">
-        <v>33973019.473</v>
+        <v>54189470.423</v>
       </c>
       <c r="J15">
-        <v>27897085.234</v>
+        <v>47326661.361</v>
       </c>
       <c r="K15">
-        <v>40192686.859</v>
+        <v>61180520.443</v>
       </c>
       <c r="L15">
-        <v>416491556.891</v>
+        <v>734545449.577</v>
       </c>
       <c r="M15">
-        <v>358329159.424</v>
+        <v>663765127.553</v>
       </c>
       <c r="N15">
-        <v>476607849.154</v>
+        <v>807677453.1160001</v>
       </c>
     </row>
     <row r="16">
@@ -1110,40 +1110,40 @@
         </is>
       </c>
       <c r="C16">
-        <v>4693.013</v>
+        <v>6543.415</v>
       </c>
       <c r="D16">
-        <v>4175.498</v>
+        <v>5954.712</v>
       </c>
       <c r="E16">
-        <v>5217</v>
+        <v>7137.352</v>
       </c>
       <c r="F16">
-        <v>7650.865</v>
+        <v>11338.719</v>
       </c>
       <c r="G16">
-        <v>6923.502</v>
+        <v>10506.971</v>
       </c>
       <c r="H16">
-        <v>8393.128000000001</v>
+        <v>12184.02</v>
       </c>
       <c r="I16">
-        <v>79022728.59</v>
+        <v>110187262.65</v>
       </c>
       <c r="J16">
-        <v>70317892.15700001</v>
+        <v>100273396.118</v>
       </c>
       <c r="K16">
-        <v>87878698.911</v>
+        <v>120260463.698</v>
       </c>
       <c r="L16">
-        <v>1017826974.378</v>
+        <v>1508452733.675</v>
       </c>
       <c r="M16">
-        <v>920673598.3559999</v>
+        <v>1397435966.812</v>
       </c>
       <c r="N16">
-        <v>1116328638.231</v>
+        <v>1620408894.188</v>
       </c>
     </row>
     <row r="17">
@@ -1158,22 +1158,22 @@
         </is>
       </c>
       <c r="C17">
-        <v>20406.012</v>
+        <v>30571.895</v>
       </c>
       <c r="D17">
-        <v>18160.402</v>
+        <v>27935.269</v>
       </c>
       <c r="E17">
-        <v>22739.956</v>
+        <v>33304.491</v>
       </c>
       <c r="F17">
-        <v>5798.821</v>
+        <v>9158.359</v>
       </c>
       <c r="G17">
-        <v>4871.96</v>
+        <v>8027.202</v>
       </c>
       <c r="H17">
-        <v>6843.454</v>
+        <v>10405.255</v>
       </c>
       <c r="I17">
         <v>0</v>
@@ -1185,13 +1185,13 @@
         <v>0</v>
       </c>
       <c r="L17">
-        <v>771241764.448</v>
+        <v>1218117987.226</v>
       </c>
       <c r="M17">
-        <v>648025897.766</v>
+        <v>1067625703.747</v>
       </c>
       <c r="N17">
-        <v>909892711.029</v>
+        <v>1384341413.386</v>
       </c>
     </row>
     <row r="18">
@@ -1206,22 +1206,22 @@
         </is>
       </c>
       <c r="C18">
-        <v>15202.821</v>
+        <v>25994.304</v>
       </c>
       <c r="D18">
-        <v>13483.852</v>
+        <v>23952.951</v>
       </c>
       <c r="E18">
-        <v>16940.515</v>
+        <v>28050.902</v>
       </c>
       <c r="F18">
-        <v>4433.81</v>
+        <v>7831.588</v>
       </c>
       <c r="G18">
-        <v>3793.325</v>
+        <v>7050.549</v>
       </c>
       <c r="H18">
-        <v>5100.817</v>
+        <v>8639.73</v>
       </c>
       <c r="I18">
         <v>0</v>
@@ -1233,13 +1233,13 @@
         <v>0</v>
       </c>
       <c r="L18">
-        <v>589881141.766</v>
+        <v>1041886858.591</v>
       </c>
       <c r="M18">
-        <v>504695756.451</v>
+        <v>937609018.223</v>
       </c>
       <c r="N18">
-        <v>678737074.369</v>
+        <v>1149686715.113</v>
       </c>
     </row>
     <row r="19">
@@ -1254,22 +1254,22 @@
         </is>
       </c>
       <c r="C19">
-        <v>42430.879</v>
+        <v>69380.766</v>
       </c>
       <c r="D19">
-        <v>39401.727</v>
+        <v>65632.546</v>
       </c>
       <c r="E19">
-        <v>45485.341</v>
+        <v>73170.717</v>
       </c>
       <c r="F19">
-        <v>13891.881</v>
+        <v>23998.068</v>
       </c>
       <c r="G19">
-        <v>12607.072</v>
+        <v>22319.579</v>
       </c>
       <c r="H19">
-        <v>15216.2</v>
+        <v>25720.649</v>
       </c>
       <c r="I19">
         <v>0</v>
@@ -1281,13 +1281,13 @@
         <v>0</v>
       </c>
       <c r="L19">
-        <v>1848067351.039</v>
+        <v>3192408477.905</v>
       </c>
       <c r="M19">
-        <v>1678184552.296</v>
+        <v>2969204899.574</v>
       </c>
       <c r="N19">
-        <v>2024141742.989</v>
+        <v>3421886115.882</v>
       </c>
     </row>
     <row r="20">
@@ -1297,40 +1297,40 @@
         </is>
       </c>
       <c r="C20">
-        <v>138167.968</v>
+        <v>217619.205</v>
       </c>
       <c r="D20">
-        <v>124486.43</v>
+        <v>201476.22</v>
       </c>
       <c r="E20">
-        <v>152180.848</v>
+        <v>234112.127</v>
       </c>
       <c r="F20">
-        <v>97671.95999999999</v>
+        <v>159673.139</v>
       </c>
       <c r="G20">
-        <v>86384.337</v>
+        <v>145892.626</v>
       </c>
       <c r="H20">
-        <v>109617.022</v>
+        <v>174145.266</v>
       </c>
       <c r="I20">
-        <v>2233076837.258</v>
+        <v>3413905202.776</v>
       </c>
       <c r="J20">
-        <v>1991093962.463</v>
+        <v>3134723128.795</v>
       </c>
       <c r="K20">
-        <v>2480720358.77</v>
+        <v>3698762160.615</v>
       </c>
       <c r="L20">
-        <v>12990603458.578</v>
+        <v>21237111135.783</v>
       </c>
       <c r="M20">
-        <v>11490292472.929</v>
+        <v>19405039461.573</v>
       </c>
       <c r="N20">
-        <v>14578277100.391</v>
+        <v>23162717570.877</v>
       </c>
     </row>
     <row r="21">
@@ -1340,40 +1340,40 @@
         </is>
       </c>
       <c r="C21">
-        <v>175249.524</v>
+        <v>276112.127</v>
       </c>
       <c r="D21">
-        <v>157099.481</v>
+        <v>254826.115</v>
       </c>
       <c r="E21">
-        <v>193722.239</v>
+        <v>297736.8180000001</v>
       </c>
       <c r="F21">
-        <v>439375.907</v>
+        <v>764403.532</v>
       </c>
       <c r="G21">
-        <v>401023.355</v>
+        <v>716822.4040000002</v>
       </c>
       <c r="H21">
-        <v>478466.672</v>
+        <v>812769.2289999999</v>
       </c>
       <c r="I21">
-        <v>2233076837.258</v>
+        <v>3413905202.776</v>
       </c>
       <c r="J21">
-        <v>1991093962.463</v>
+        <v>3134723128.795</v>
       </c>
       <c r="K21">
-        <v>2480720358.77</v>
+        <v>3698762160.615</v>
       </c>
       <c r="L21">
-        <v>58440210619.465</v>
+        <v>101670527022.612</v>
       </c>
       <c r="M21">
-        <v>53323787871.166</v>
+        <v>95326932709.70702</v>
       </c>
       <c r="N21">
-        <v>63658273569.39402</v>
+        <v>108130473702.172</v>
       </c>
     </row>
   </sheetData>

--- a/output/Tables/Best practice/Residence/HIA_area_2019_1000replicate_RES.xlsx
+++ b/output/Tables/Best practice/Residence/HIA_area_2019_1000replicate_RES.xlsx
@@ -1,21 +1,120 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <fileVersion appName="xl" lastEdited="4" lowestEdited="4" rupBuild="4505"/>
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="4" rupBuild="10119"/>
   <workbookPr defaultThemeVersion="124226"/>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice Requires="x15">
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/ines/Documents/PhD/PROJETS/MARCHE/HIA_walking_steps/output/Tables/Best practice/Residence/"/>
+    </mc:Choice>
+  </mc:AlternateContent>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{9C367C58-EC0C-3C4E-8AAD-54FF51AFE991}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="240" yWindow="15" windowWidth="16095" windowHeight="9660"/>
+    <workbookView xWindow="240" yWindow="500" windowWidth="26320" windowHeight="15140" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
   </sheets>
-  <calcPr calcId="124519" fullCalcOnLoad="1"/>
+  <calcPr calcId="191029"/>
+  <extLst>
+    <ext xmlns:xcalcf="http://schemas.microsoft.com/office/spreadsheetml/2018/calcfeatures" uri="{B58B0392-4F1F-4190-BB64-5DF3571DCE5F}">
+      <xcalcf:calcFeatures>
+        <xcalcf:feature name="microsoft.com:RD"/>
+        <xcalcf:feature name="microsoft.com:Single"/>
+        <xcalcf:feature name="microsoft.com:FV"/>
+        <xcalcf:feature name="microsoft.com:CNMTM"/>
+        <xcalcf:feature name="microsoft.com:LET_WF"/>
+        <xcalcf:feature name="microsoft.com:LAMBDA_WF"/>
+        <xcalcf:feature name="microsoft.com:ARRAYTEXT_WF"/>
+      </xcalcf:calcFeatures>
+    </ext>
+  </extLst>
 </workbook>
 </file>
 
+<file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="52" uniqueCount="25">
+  <si>
+    <t>disease</t>
+  </si>
+  <si>
+    <t>area_type</t>
+  </si>
+  <si>
+    <t>tot_cases</t>
+  </si>
+  <si>
+    <t>tot_cases_low</t>
+  </si>
+  <si>
+    <t>tot_cases_up</t>
+  </si>
+  <si>
+    <t>tot_daly</t>
+  </si>
+  <si>
+    <t>tot_daly_low</t>
+  </si>
+  <si>
+    <t>tot_daly_up</t>
+  </si>
+  <si>
+    <t>tot_medic_costs</t>
+  </si>
+  <si>
+    <t>tot_medic_costs_low</t>
+  </si>
+  <si>
+    <t>tot_medic_costs_up</t>
+  </si>
+  <si>
+    <t>tot_soc_costs</t>
+  </si>
+  <si>
+    <t>tot_soc_costs_low</t>
+  </si>
+  <si>
+    <t>tot_soc_costs_up</t>
+  </si>
+  <si>
+    <t>mort</t>
+  </si>
+  <si>
+    <t>periurban</t>
+  </si>
+  <si>
+    <t>rural</t>
+  </si>
+  <si>
+    <t>urban</t>
+  </si>
+  <si>
+    <t>cvd</t>
+  </si>
+  <si>
+    <t>cancer</t>
+  </si>
+  <si>
+    <t>diab2</t>
+  </si>
+  <si>
+    <t>dem</t>
+  </si>
+  <si>
+    <t>dep</t>
+  </si>
+  <si>
+    <t>Morbidity</t>
+  </si>
+  <si>
+    <t>All</t>
+  </si>
+</sst>
+</file>
+
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
-<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <fonts count="2">
+<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
+  <fonts count="2" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -63,13 +162,21 @@
   </cellStyles>
   <dxfs count="0"/>
   <tableStyles count="0" defaultTableStyle="TableStyleMedium9" defaultPivotStyle="PivotStyleLight16"/>
+  <extLst>
+    <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{EB79DEF2-80B8-43e5-95BD-54CBDDF9020C}">
+      <x14:slicerStyles defaultSlicerStyle="SlicerStyleLight1"/>
+    </ext>
+    <ext xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" uri="{9260A510-F301-46a8-8635-F512D64BE5F5}">
+      <x15:timelineStyles defaultTimelineStyle="TimeSlicerStyleLight1"/>
+    </ext>
+  </extLst>
 </styleSheet>
 </file>
 
 <file path=xl/theme/theme1.xml><?xml version="1.0" encoding="utf-8"?>
-<a:theme xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" name="Office Theme">
+<a:theme xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" name="Office Theme 2007 - 2010">
   <a:themeElements>
-    <a:clrScheme name="Office">
+    <a:clrScheme name="Office 2007 - 2010">
       <a:dk1>
         <a:sysClr val="windowText" lastClr="000000"/>
       </a:dk1>
@@ -107,7 +214,7 @@
         <a:srgbClr val="800080"/>
       </a:folHlink>
     </a:clrScheme>
-    <a:fontScheme name="Office">
+    <a:fontScheme name="Office 2007 - 2010">
       <a:majorFont>
         <a:latin typeface="Cambria"/>
         <a:ea typeface=""/>
@@ -141,6 +248,7 @@
         <a:font script="Mong" typeface="Mongolian Baiti"/>
         <a:font script="Viet" typeface="Times New Roman"/>
         <a:font script="Uigh" typeface="Microsoft Uighur"/>
+        <a:font script="Geor" typeface="Sylfaen"/>
       </a:majorFont>
       <a:minorFont>
         <a:latin typeface="Calibri"/>
@@ -175,9 +283,10 @@
         <a:font script="Mong" typeface="Mongolian Baiti"/>
         <a:font script="Viet" typeface="Arial"/>
         <a:font script="Uigh" typeface="Microsoft Uighur"/>
+        <a:font script="Geor" typeface="Sylfaen"/>
       </a:minorFont>
     </a:fontScheme>
-    <a:fmtScheme name="Office">
+    <a:fmtScheme name="Office 2007 - 2010">
       <a:fillStyleLst>
         <a:solidFill>
           <a:schemeClr val="phClr"/>
@@ -350,104 +459,83 @@
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
   <dimension ref="A1:N21"/>
-  <sheetFormatPr defaultRowHeight="15"/>
+  <sheetFormatPr baseColWidth="10" defaultColWidth="8.83203125" defaultRowHeight="15" x14ac:dyDescent="0.2"/>
+  <cols>
+    <col min="3" max="3" width="11.1640625" bestFit="1" customWidth="1"/>
+    <col min="4" max="4" width="12" bestFit="1" customWidth="1"/>
+    <col min="5" max="8" width="11.1640625" bestFit="1" customWidth="1"/>
+    <col min="9" max="9" width="13.83203125" bestFit="1" customWidth="1"/>
+    <col min="10" max="10" width="17.6640625" bestFit="1" customWidth="1"/>
+    <col min="11" max="11" width="16.83203125" bestFit="1" customWidth="1"/>
+    <col min="12" max="12" width="12.1640625" bestFit="1" customWidth="1"/>
+    <col min="13" max="13" width="15.1640625" bestFit="1" customWidth="1"/>
+    <col min="14" max="14" width="14.33203125" bestFit="1" customWidth="1"/>
+  </cols>
   <sheetData>
-    <row r="1" s="1" customFormat="1">
-      <c r="A1" s="1" t="inlineStr">
-        <is>
-          <t>disease</t>
-        </is>
-      </c>
-      <c r="B1" s="1" t="inlineStr">
-        <is>
-          <t>area_type</t>
-        </is>
-      </c>
-      <c r="C1" s="1" t="inlineStr">
-        <is>
-          <t>tot_cases</t>
-        </is>
-      </c>
-      <c r="D1" s="1" t="inlineStr">
-        <is>
-          <t>tot_cases_low</t>
-        </is>
-      </c>
-      <c r="E1" s="1" t="inlineStr">
-        <is>
-          <t>tot_cases_up</t>
-        </is>
-      </c>
-      <c r="F1" s="1" t="inlineStr">
-        <is>
-          <t>tot_daly</t>
-        </is>
-      </c>
-      <c r="G1" s="1" t="inlineStr">
-        <is>
-          <t>tot_daly_low</t>
-        </is>
-      </c>
-      <c r="H1" s="1" t="inlineStr">
-        <is>
-          <t>tot_daly_up</t>
-        </is>
-      </c>
-      <c r="I1" s="1" t="inlineStr">
-        <is>
-          <t>tot_medic_costs</t>
-        </is>
-      </c>
-      <c r="J1" s="1" t="inlineStr">
-        <is>
-          <t>tot_medic_costs_low</t>
-        </is>
-      </c>
-      <c r="K1" s="1" t="inlineStr">
-        <is>
-          <t>tot_medic_costs_up</t>
-        </is>
-      </c>
-      <c r="L1" s="1" t="inlineStr">
-        <is>
-          <t>tot_soc_costs</t>
-        </is>
-      </c>
-      <c r="M1" s="1" t="inlineStr">
-        <is>
-          <t>tot_soc_costs_low</t>
-        </is>
-      </c>
-      <c r="N1" s="1" t="inlineStr">
-        <is>
-          <t>tot_soc_costs_up</t>
-        </is>
-      </c>
-    </row>
-    <row r="2">
-      <c r="A2" t="inlineStr">
-        <is>
-          <t>mort</t>
-        </is>
-      </c>
-      <c r="B2" t="inlineStr">
-        <is>
-          <t>periurban</t>
-        </is>
+    <row r="1" spans="1:14" s="1" customFormat="1" x14ac:dyDescent="0.2">
+      <c r="A1" s="1" t="s">
+        <v>0</v>
+      </c>
+      <c r="B1" s="1" t="s">
+        <v>1</v>
+      </c>
+      <c r="C1" s="1" t="s">
+        <v>2</v>
+      </c>
+      <c r="D1" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="E1" s="1" t="s">
+        <v>4</v>
+      </c>
+      <c r="F1" s="1" t="s">
+        <v>5</v>
+      </c>
+      <c r="G1" s="1" t="s">
+        <v>6</v>
+      </c>
+      <c r="H1" s="1" t="s">
+        <v>7</v>
+      </c>
+      <c r="I1" s="1" t="s">
+        <v>8</v>
+      </c>
+      <c r="J1" s="1" t="s">
+        <v>9</v>
+      </c>
+      <c r="K1" s="1" t="s">
+        <v>10</v>
+      </c>
+      <c r="L1" s="1" t="s">
+        <v>11</v>
+      </c>
+      <c r="M1" s="1" t="s">
+        <v>12</v>
+      </c>
+      <c r="N1" s="1" t="s">
+        <v>13</v>
+      </c>
+    </row>
+    <row r="2" spans="1:14" x14ac:dyDescent="0.2">
+      <c r="A2" t="s">
+        <v>14</v>
+      </c>
+      <c r="B2" t="s">
+        <v>15</v>
       </c>
       <c r="C2">
-        <v>17297.015</v>
+        <v>17297.014999999999</v>
       </c>
       <c r="D2">
         <v>15546.688</v>
       </c>
       <c r="E2">
-        <v>19051.461</v>
+        <v>19051.460999999999</v>
       </c>
       <c r="F2">
-        <v>156123.485</v>
+        <v>156123.48499999999</v>
       </c>
       <c r="G2">
         <v>145839.976</v>
@@ -465,43 +553,39 @@
         <v>0</v>
       </c>
       <c r="L2">
-        <v>20765612100.156</v>
+        <v>20765612100.155998</v>
       </c>
       <c r="M2">
-        <v>19391149302.275</v>
+        <v>19391149302.275002</v>
       </c>
       <c r="N2">
-        <v>22139529088.148</v>
-      </c>
-    </row>
-    <row r="3">
-      <c r="A3" t="inlineStr">
-        <is>
-          <t>mort</t>
-        </is>
-      </c>
-      <c r="B3" t="inlineStr">
-        <is>
-          <t>rural</t>
-        </is>
+        <v>22139529088.147999</v>
+      </c>
+    </row>
+    <row r="3" spans="1:14" x14ac:dyDescent="0.2">
+      <c r="A3" t="s">
+        <v>14</v>
+      </c>
+      <c r="B3" t="s">
+        <v>16</v>
       </c>
       <c r="C3">
-        <v>14421.137</v>
+        <v>14421.137000000001</v>
       </c>
       <c r="D3">
-        <v>13027.762</v>
+        <v>13027.762000000001</v>
       </c>
       <c r="E3">
         <v>15809.741</v>
       </c>
       <c r="F3">
-        <v>150023.904</v>
+        <v>150023.90400000001</v>
       </c>
       <c r="G3">
-        <v>140191.306</v>
+        <v>140191.30600000001</v>
       </c>
       <c r="H3">
-        <v>159888.716</v>
+        <v>159888.71599999999</v>
       </c>
       <c r="I3">
         <v>0</v>
@@ -513,25 +597,21 @@
         <v>0</v>
       </c>
       <c r="L3">
-        <v>19950665546.293</v>
+        <v>19950665546.292999</v>
       </c>
       <c r="M3">
-        <v>18638561066.204</v>
+        <v>18638561066.203999</v>
       </c>
       <c r="N3">
-        <v>21275044775.269</v>
-      </c>
-    </row>
-    <row r="4">
-      <c r="A4" t="inlineStr">
-        <is>
-          <t>mort</t>
-        </is>
-      </c>
-      <c r="B4" t="inlineStr">
-        <is>
-          <t>urban</t>
-        </is>
+        <v>21275044775.269001</v>
+      </c>
+    </row>
+    <row r="4" spans="1:14" x14ac:dyDescent="0.2">
+      <c r="A4" t="s">
+        <v>14</v>
+      </c>
+      <c r="B4" t="s">
+        <v>17</v>
       </c>
       <c r="C4">
         <v>26774.77</v>
@@ -540,16 +620,16 @@
         <v>24775.445</v>
       </c>
       <c r="E4">
-        <v>28763.489</v>
+        <v>28763.489000000001</v>
       </c>
       <c r="F4">
-        <v>298583.004</v>
+        <v>298583.00400000002</v>
       </c>
       <c r="G4">
-        <v>284898.496</v>
+        <v>284898.49599999998</v>
       </c>
       <c r="H4">
-        <v>312266.269</v>
+        <v>312266.26899999997</v>
       </c>
       <c r="I4">
         <v>0</v>
@@ -561,100 +641,92 @@
         <v>0</v>
       </c>
       <c r="L4">
-        <v>39717138240.38</v>
+        <v>39717138240.379997</v>
       </c>
       <c r="M4">
-        <v>37892182879.655</v>
+        <v>37892182879.654999</v>
       </c>
       <c r="N4">
-        <v>41553182267.878</v>
-      </c>
-    </row>
-    <row r="5">
-      <c r="A5" t="inlineStr">
-        <is>
-          <t>cvd</t>
-        </is>
-      </c>
-      <c r="B5" t="inlineStr">
-        <is>
-          <t>periurban</t>
-        </is>
+        <v>41553182267.877998</v>
+      </c>
+    </row>
+    <row r="5" spans="1:14" x14ac:dyDescent="0.2">
+      <c r="A5" t="s">
+        <v>18</v>
+      </c>
+      <c r="B5" t="s">
+        <v>15</v>
       </c>
       <c r="C5">
-        <v>11472.925</v>
+        <v>11472.924999999999</v>
       </c>
       <c r="D5">
-        <v>10435.808</v>
+        <v>10435.808000000001</v>
       </c>
       <c r="E5">
-        <v>12524.763</v>
+        <v>12524.763000000001</v>
       </c>
       <c r="F5">
-        <v>9321.355</v>
+        <v>9321.3549999999996</v>
       </c>
       <c r="G5">
         <v>8541.73</v>
       </c>
       <c r="H5">
-        <v>10112.54</v>
+        <v>10112.540000000001</v>
       </c>
       <c r="I5">
-        <v>639083997.099</v>
+        <v>639083997.09899998</v>
       </c>
       <c r="J5">
-        <v>581084801.827</v>
+        <v>581084801.82700002</v>
       </c>
       <c r="K5">
-        <v>697712548.822</v>
+        <v>697712548.82200003</v>
       </c>
       <c r="L5">
-        <v>1239723582.979</v>
+        <v>1239723582.9790001</v>
       </c>
       <c r="M5">
-        <v>1135789542.261</v>
+        <v>1135789542.2609999</v>
       </c>
       <c r="N5">
-        <v>1345159125.143</v>
-      </c>
-    </row>
-    <row r="6">
-      <c r="A6" t="inlineStr">
-        <is>
-          <t>cvd</t>
-        </is>
-      </c>
-      <c r="B6" t="inlineStr">
-        <is>
-          <t>rural</t>
-        </is>
+        <v>1345159125.1429999</v>
+      </c>
+    </row>
+    <row r="6" spans="1:14" x14ac:dyDescent="0.2">
+      <c r="A6" t="s">
+        <v>18</v>
+      </c>
+      <c r="B6" t="s">
+        <v>16</v>
       </c>
       <c r="C6">
-        <v>9713.377</v>
+        <v>9713.3770000000004</v>
       </c>
       <c r="D6">
-        <v>8827.186</v>
+        <v>8827.1859999999997</v>
       </c>
       <c r="E6">
         <v>10613.922</v>
       </c>
       <c r="F6">
-        <v>8712.075999999999</v>
+        <v>8712.0759999999991</v>
       </c>
       <c r="G6">
         <v>7948.56</v>
       </c>
       <c r="H6">
-        <v>9497.772000000001</v>
+        <v>9497.7720000000008</v>
       </c>
       <c r="I6">
-        <v>541206377.4170001</v>
+        <v>541206377.41700006</v>
       </c>
       <c r="J6">
-        <v>491723496.443</v>
+        <v>491723496.44300002</v>
       </c>
       <c r="K6">
-        <v>591471577.337</v>
+        <v>591471577.33700001</v>
       </c>
       <c r="L6">
         <v>1159009885.987</v>
@@ -666,16 +738,12 @@
         <v>1263354825.243</v>
       </c>
     </row>
-    <row r="7">
-      <c r="A7" t="inlineStr">
-        <is>
-          <t>cvd</t>
-        </is>
-      </c>
-      <c r="B7" t="inlineStr">
-        <is>
-          <t>urban</t>
-        </is>
+    <row r="7" spans="1:14" x14ac:dyDescent="0.2">
+      <c r="A7" t="s">
+        <v>18</v>
+      </c>
+      <c r="B7" t="s">
+        <v>17</v>
       </c>
       <c r="C7">
         <v>18947.677</v>
@@ -684,13 +752,13 @@
         <v>17723.088</v>
       </c>
       <c r="E7">
-        <v>20182.937</v>
+        <v>20182.937000000002</v>
       </c>
       <c r="F7">
-        <v>17888.351</v>
+        <v>17888.350999999999</v>
       </c>
       <c r="G7">
-        <v>16861.307</v>
+        <v>16861.307000000001</v>
       </c>
       <c r="H7">
         <v>18927.608</v>
@@ -699,55 +767,51 @@
         <v>1055517058.74</v>
       </c>
       <c r="J7">
-        <v>987045327.9400001</v>
+        <v>987045327.94000006</v>
       </c>
       <c r="K7">
-        <v>1124508490.134</v>
+        <v>1124508490.1340001</v>
       </c>
       <c r="L7">
-        <v>2379377282.076</v>
+        <v>2379377282.0760002</v>
       </c>
       <c r="M7">
-        <v>2242452418.479</v>
+        <v>2242452418.4790001</v>
       </c>
       <c r="N7">
-        <v>2517129625.951</v>
-      </c>
-    </row>
-    <row r="8">
-      <c r="A8" t="inlineStr">
-        <is>
-          <t>cancer</t>
-        </is>
-      </c>
-      <c r="B8" t="inlineStr">
-        <is>
-          <t>periurban</t>
-        </is>
+        <v>2517129625.9510002</v>
+      </c>
+    </row>
+    <row r="8" spans="1:14" x14ac:dyDescent="0.2">
+      <c r="A8" t="s">
+        <v>19</v>
+      </c>
+      <c r="B8" t="s">
+        <v>15</v>
       </c>
       <c r="C8">
-        <v>8092.691</v>
+        <v>8092.6909999999998</v>
       </c>
       <c r="D8">
-        <v>7286.138</v>
+        <v>7286.1379999999999</v>
       </c>
       <c r="E8">
-        <v>8935.870999999999</v>
+        <v>8935.8709999999992</v>
       </c>
       <c r="F8">
-        <v>11163.711</v>
+        <v>11163.710999999999</v>
       </c>
       <c r="G8">
-        <v>9772.101000000001</v>
+        <v>9772.1010000000006</v>
       </c>
       <c r="H8">
-        <v>12720.468</v>
+        <v>12720.468000000001</v>
       </c>
       <c r="I8">
         <v>119799970.005</v>
       </c>
       <c r="J8">
-        <v>107881367.136</v>
+        <v>107881367.13600001</v>
       </c>
       <c r="K8">
         <v>132329000.068</v>
@@ -762,19 +826,15 @@
         <v>1691703090.908</v>
       </c>
     </row>
-    <row r="9">
-      <c r="A9" t="inlineStr">
-        <is>
-          <t>cancer</t>
-        </is>
-      </c>
-      <c r="B9" t="inlineStr">
-        <is>
-          <t>rural</t>
-        </is>
+    <row r="9" spans="1:14" x14ac:dyDescent="0.2">
+      <c r="A9" t="s">
+        <v>19</v>
+      </c>
+      <c r="B9" t="s">
+        <v>16</v>
       </c>
       <c r="C9">
-        <v>6844.618</v>
+        <v>6844.6180000000004</v>
       </c>
       <c r="D9">
         <v>6181.848</v>
@@ -786,16 +846,16 @@
         <v>9568.643</v>
       </c>
       <c r="G9">
-        <v>8494.361000000001</v>
+        <v>8494.3610000000008</v>
       </c>
       <c r="H9">
         <v>10734.445</v>
       </c>
       <c r="I9">
-        <v>101309575.762</v>
+        <v>101309575.76199999</v>
       </c>
       <c r="J9">
-        <v>91513640.325</v>
+        <v>91513640.325000003</v>
       </c>
       <c r="K9">
         <v>111672984.301</v>
@@ -804,88 +864,80 @@
         <v>1272156968.585</v>
       </c>
       <c r="M9">
-        <v>1130083001.31</v>
+        <v>1130083001.3099999</v>
       </c>
       <c r="N9">
         <v>1427687095.546</v>
       </c>
     </row>
-    <row r="10">
-      <c r="A10" t="inlineStr">
-        <is>
-          <t>cancer</t>
-        </is>
-      </c>
-      <c r="B10" t="inlineStr">
-        <is>
-          <t>urban</t>
-        </is>
+    <row r="10" spans="1:14" x14ac:dyDescent="0.2">
+      <c r="A10" t="s">
+        <v>19</v>
+      </c>
+      <c r="B10" t="s">
+        <v>17</v>
       </c>
       <c r="C10">
         <v>16267.713</v>
       </c>
       <c r="D10">
-        <v>15186.183</v>
+        <v>15186.183000000001</v>
       </c>
       <c r="E10">
         <v>17394.517</v>
       </c>
       <c r="F10">
-        <v>26280.255</v>
+        <v>26280.255000000001</v>
       </c>
       <c r="G10">
         <v>24223.909</v>
       </c>
       <c r="H10">
-        <v>28451.792</v>
+        <v>28451.792000000001</v>
       </c>
       <c r="I10">
-        <v>240891229.837</v>
+        <v>240891229.83700001</v>
       </c>
       <c r="J10">
-        <v>224859849.878</v>
+        <v>224859849.87799999</v>
       </c>
       <c r="K10">
-        <v>257653995.721</v>
+        <v>257653995.72099999</v>
       </c>
       <c r="L10">
-        <v>3494967615.946</v>
+        <v>3494967615.9460001</v>
       </c>
       <c r="M10">
-        <v>3222948265.595</v>
+        <v>3222948265.5949998</v>
       </c>
       <c r="N10">
-        <v>3783553944.516</v>
-      </c>
-    </row>
-    <row r="11">
-      <c r="A11" t="inlineStr">
-        <is>
-          <t>diab2</t>
-        </is>
-      </c>
-      <c r="B11" t="inlineStr">
-        <is>
-          <t>periurban</t>
-        </is>
+        <v>3783553944.5159998</v>
+      </c>
+    </row>
+    <row r="11" spans="1:14" x14ac:dyDescent="0.2">
+      <c r="A11" t="s">
+        <v>20</v>
+      </c>
+      <c r="B11" t="s">
+        <v>15</v>
       </c>
       <c r="C11">
         <v>1600.047</v>
       </c>
       <c r="D11">
-        <v>1437.474</v>
+        <v>1437.4739999999999</v>
       </c>
       <c r="E11">
         <v>1770.453</v>
       </c>
       <c r="F11">
-        <v>2861.881</v>
+        <v>2861.8809999999999</v>
       </c>
       <c r="G11">
-        <v>2563.253</v>
+        <v>2563.2530000000002</v>
       </c>
       <c r="H11">
-        <v>3174.396</v>
+        <v>3174.3960000000002</v>
       </c>
       <c r="I11">
         <v>120341117.529</v>
@@ -897,28 +949,24 @@
         <v>133122961.199</v>
       </c>
       <c r="L11">
-        <v>380643427.115</v>
+        <v>380643427.11500001</v>
       </c>
       <c r="M11">
-        <v>340935925.642</v>
+        <v>340935925.64200002</v>
       </c>
       <c r="N11">
-        <v>422261729.862</v>
-      </c>
-    </row>
-    <row r="12">
-      <c r="A12" t="inlineStr">
-        <is>
-          <t>diab2</t>
-        </is>
-      </c>
-      <c r="B12" t="inlineStr">
-        <is>
-          <t>rural</t>
-        </is>
+        <v>422261729.86199999</v>
+      </c>
+    </row>
+    <row r="12" spans="1:14" x14ac:dyDescent="0.2">
+      <c r="A12" t="s">
+        <v>20</v>
+      </c>
+      <c r="B12" t="s">
+        <v>16</v>
       </c>
       <c r="C12">
-        <v>1440.782</v>
+        <v>1440.7819999999999</v>
       </c>
       <c r="D12">
         <v>1293.136</v>
@@ -927,148 +975,136 @@
         <v>1594.855</v>
       </c>
       <c r="F12">
-        <v>2647.575</v>
+        <v>2647.5749999999998</v>
       </c>
       <c r="G12">
-        <v>2369.506</v>
+        <v>2369.5059999999999</v>
       </c>
       <c r="H12">
         <v>2939.902</v>
       </c>
       <c r="I12">
-        <v>108370155.887</v>
+        <v>108370155.88699999</v>
       </c>
       <c r="J12">
-        <v>97336795.15099999</v>
+        <v>97336795.150999993</v>
       </c>
       <c r="K12">
         <v>119918234.013</v>
       </c>
       <c r="L12">
-        <v>352030795.456</v>
+        <v>352030795.45599997</v>
       </c>
       <c r="M12">
-        <v>315312476.419</v>
+        <v>315312476.41900003</v>
       </c>
       <c r="N12">
-        <v>390860248.244</v>
-      </c>
-    </row>
-    <row r="13">
-      <c r="A13" t="inlineStr">
-        <is>
-          <t>diab2</t>
-        </is>
-      </c>
-      <c r="B13" t="inlineStr">
-        <is>
-          <t>urban</t>
-        </is>
+        <v>390860248.24400002</v>
+      </c>
+    </row>
+    <row r="13" spans="1:14" x14ac:dyDescent="0.2">
+      <c r="A13" t="s">
+        <v>20</v>
+      </c>
+      <c r="B13" t="s">
+        <v>17</v>
       </c>
       <c r="C13">
-        <v>3361.316</v>
+        <v>3361.3159999999998</v>
       </c>
       <c r="D13">
-        <v>3132.525</v>
+        <v>3132.5250000000001</v>
       </c>
       <c r="E13">
         <v>3596.252</v>
       </c>
       <c r="F13">
-        <v>6991.624</v>
+        <v>6991.6239999999998</v>
       </c>
       <c r="G13">
         <v>6501.268</v>
       </c>
       <c r="H13">
-        <v>7501.719</v>
+        <v>7501.7190000000001</v>
       </c>
       <c r="I13">
-        <v>252797211.378</v>
+        <v>252797211.37799999</v>
       </c>
       <c r="J13">
         <v>235549603.588</v>
       </c>
       <c r="K13">
-        <v>270469842.189</v>
+        <v>270469842.18900001</v>
       </c>
       <c r="L13">
-        <v>929753252.064</v>
+        <v>929753252.06400001</v>
       </c>
       <c r="M13">
         <v>864354678.102</v>
       </c>
       <c r="N13">
-        <v>997489931.5650001</v>
-      </c>
-    </row>
-    <row r="14">
-      <c r="A14" t="inlineStr">
-        <is>
-          <t>dem</t>
-        </is>
-      </c>
-      <c r="B14" t="inlineStr">
-        <is>
-          <t>periurban</t>
-        </is>
+        <v>997489931.56500006</v>
+      </c>
+    </row>
+    <row r="14" spans="1:14" x14ac:dyDescent="0.2">
+      <c r="A14" t="s">
+        <v>21</v>
+      </c>
+      <c r="B14" t="s">
+        <v>15</v>
       </c>
       <c r="C14">
-        <v>4169.365</v>
+        <v>4169.3649999999998</v>
       </c>
       <c r="D14">
         <v>3685.52</v>
       </c>
       <c r="E14">
-        <v>4658.943</v>
+        <v>4658.9430000000002</v>
       </c>
       <c r="F14">
-        <v>6387.084</v>
+        <v>6387.0839999999998</v>
       </c>
       <c r="G14">
-        <v>5724.156</v>
+        <v>5724.1559999999999</v>
       </c>
       <c r="H14">
-        <v>7064.649</v>
+        <v>7064.6490000000003</v>
       </c>
       <c r="I14">
-        <v>70211776.04899999</v>
+        <v>70211776.048999995</v>
       </c>
       <c r="J14">
-        <v>62094856.609</v>
+        <v>62094856.608999997</v>
       </c>
       <c r="K14">
-        <v>78461542.69</v>
+        <v>78461542.689999998</v>
       </c>
       <c r="L14">
-        <v>849464958.663</v>
+        <v>849464958.66299999</v>
       </c>
       <c r="M14">
-        <v>760911541.575</v>
+        <v>760911541.57500005</v>
       </c>
       <c r="N14">
-        <v>939517362.214</v>
-      </c>
-    </row>
-    <row r="15">
-      <c r="A15" t="inlineStr">
-        <is>
-          <t>dem</t>
-        </is>
-      </c>
-      <c r="B15" t="inlineStr">
-        <is>
-          <t>rural</t>
-        </is>
+        <v>939517362.21399999</v>
+      </c>
+    </row>
+    <row r="15" spans="1:14" x14ac:dyDescent="0.2">
+      <c r="A15" t="s">
+        <v>21</v>
+      </c>
+      <c r="B15" t="s">
+        <v>16</v>
       </c>
       <c r="C15">
-        <v>3218.314</v>
+        <v>3218.3139999999999</v>
       </c>
       <c r="D15">
-        <v>2811.836</v>
+        <v>2811.8359999999998</v>
       </c>
       <c r="E15">
-        <v>3636.602</v>
+        <v>3636.6019999999999</v>
       </c>
       <c r="F15">
         <v>5523.85</v>
@@ -1077,49 +1113,45 @@
         <v>4988.174</v>
       </c>
       <c r="H15">
-        <v>6070.321</v>
+        <v>6070.3209999999999</v>
       </c>
       <c r="I15">
         <v>54189470.423</v>
       </c>
       <c r="J15">
-        <v>47326661.361</v>
+        <v>47326661.361000001</v>
       </c>
       <c r="K15">
-        <v>61180520.443</v>
+        <v>61180520.443000004</v>
       </c>
       <c r="L15">
-        <v>734545449.577</v>
+        <v>734545449.57700002</v>
       </c>
       <c r="M15">
-        <v>663765127.553</v>
+        <v>663765127.55299997</v>
       </c>
       <c r="N15">
-        <v>807677453.1160001</v>
-      </c>
-    </row>
-    <row r="16">
-      <c r="A16" t="inlineStr">
-        <is>
-          <t>dem</t>
-        </is>
-      </c>
-      <c r="B16" t="inlineStr">
-        <is>
-          <t>urban</t>
-        </is>
+        <v>807677453.11600006</v>
+      </c>
+    </row>
+    <row r="16" spans="1:14" x14ac:dyDescent="0.2">
+      <c r="A16" t="s">
+        <v>21</v>
+      </c>
+      <c r="B16" t="s">
+        <v>17</v>
       </c>
       <c r="C16">
         <v>6543.415</v>
       </c>
       <c r="D16">
-        <v>5954.712</v>
+        <v>5954.7120000000004</v>
       </c>
       <c r="E16">
-        <v>7137.352</v>
+        <v>7137.3519999999999</v>
       </c>
       <c r="F16">
-        <v>11338.719</v>
+        <v>11338.718999999999</v>
       </c>
       <c r="G16">
         <v>10506.971</v>
@@ -1128,7 +1160,7 @@
         <v>12184.02</v>
       </c>
       <c r="I16">
-        <v>110187262.65</v>
+        <v>110187262.65000001</v>
       </c>
       <c r="J16">
         <v>100273396.118</v>
@@ -1146,16 +1178,12 @@
         <v>1620408894.188</v>
       </c>
     </row>
-    <row r="17">
-      <c r="A17" t="inlineStr">
-        <is>
-          <t>dep</t>
-        </is>
-      </c>
-      <c r="B17" t="inlineStr">
-        <is>
-          <t>periurban</t>
-        </is>
+    <row r="17" spans="1:14" x14ac:dyDescent="0.2">
+      <c r="A17" t="s">
+        <v>22</v>
+      </c>
+      <c r="B17" t="s">
+        <v>15</v>
       </c>
       <c r="C17">
         <v>30571.895</v>
@@ -1164,16 +1192,16 @@
         <v>27935.269</v>
       </c>
       <c r="E17">
-        <v>33304.491</v>
+        <v>33304.491000000002</v>
       </c>
       <c r="F17">
-        <v>9158.359</v>
+        <v>9158.3590000000004</v>
       </c>
       <c r="G17">
-        <v>8027.202</v>
+        <v>8027.2020000000002</v>
       </c>
       <c r="H17">
-        <v>10405.255</v>
+        <v>10405.254999999999</v>
       </c>
       <c r="I17">
         <v>0</v>
@@ -1185,37 +1213,33 @@
         <v>0</v>
       </c>
       <c r="L17">
-        <v>1218117987.226</v>
+        <v>1218117987.2260001</v>
       </c>
       <c r="M17">
         <v>1067625703.747</v>
       </c>
       <c r="N17">
-        <v>1384341413.386</v>
-      </c>
-    </row>
-    <row r="18">
-      <c r="A18" t="inlineStr">
-        <is>
-          <t>dep</t>
-        </is>
-      </c>
-      <c r="B18" t="inlineStr">
-        <is>
-          <t>rural</t>
-        </is>
+        <v>1384341413.3859999</v>
+      </c>
+    </row>
+    <row r="18" spans="1:14" x14ac:dyDescent="0.2">
+      <c r="A18" t="s">
+        <v>22</v>
+      </c>
+      <c r="B18" t="s">
+        <v>16</v>
       </c>
       <c r="C18">
         <v>25994.304</v>
       </c>
       <c r="D18">
-        <v>23952.951</v>
+        <v>23952.951000000001</v>
       </c>
       <c r="E18">
-        <v>28050.902</v>
+        <v>28050.901999999998</v>
       </c>
       <c r="F18">
-        <v>7831.588</v>
+        <v>7831.5879999999997</v>
       </c>
       <c r="G18">
         <v>7050.549</v>
@@ -1236,40 +1260,36 @@
         <v>1041886858.591</v>
       </c>
       <c r="M18">
-        <v>937609018.223</v>
+        <v>937609018.22300005</v>
       </c>
       <c r="N18">
-        <v>1149686715.113</v>
-      </c>
-    </row>
-    <row r="19">
-      <c r="A19" t="inlineStr">
-        <is>
-          <t>dep</t>
-        </is>
-      </c>
-      <c r="B19" t="inlineStr">
-        <is>
-          <t>urban</t>
-        </is>
+        <v>1149686715.1129999</v>
+      </c>
+    </row>
+    <row r="19" spans="1:14" x14ac:dyDescent="0.2">
+      <c r="A19" t="s">
+        <v>22</v>
+      </c>
+      <c r="B19" t="s">
+        <v>17</v>
       </c>
       <c r="C19">
-        <v>69380.766</v>
+        <v>69380.766000000003</v>
       </c>
       <c r="D19">
-        <v>65632.546</v>
+        <v>65632.546000000002</v>
       </c>
       <c r="E19">
-        <v>73170.717</v>
+        <v>73170.717000000004</v>
       </c>
       <c r="F19">
-        <v>23998.068</v>
+        <v>23998.067999999999</v>
       </c>
       <c r="G19">
-        <v>22319.579</v>
+        <v>22319.579000000002</v>
       </c>
       <c r="H19">
-        <v>25720.649</v>
+        <v>25720.649000000001</v>
       </c>
       <c r="I19">
         <v>0</v>
@@ -1281,35 +1301,33 @@
         <v>0</v>
       </c>
       <c r="L19">
-        <v>3192408477.905</v>
+        <v>3192408477.9050002</v>
       </c>
       <c r="M19">
-        <v>2969204899.574</v>
+        <v>2969204899.5739999</v>
       </c>
       <c r="N19">
         <v>3421886115.882</v>
       </c>
     </row>
-    <row r="20">
-      <c r="A20" t="inlineStr">
-        <is>
-          <t>Morbidity</t>
-        </is>
+    <row r="20" spans="1:14" x14ac:dyDescent="0.2">
+      <c r="A20" t="s">
+        <v>23</v>
       </c>
       <c r="C20">
-        <v>217619.205</v>
+        <v>217619.20499999999</v>
       </c>
       <c r="D20">
         <v>201476.22</v>
       </c>
       <c r="E20">
-        <v>234112.127</v>
+        <v>234112.12700000001</v>
       </c>
       <c r="F20">
         <v>159673.139</v>
       </c>
       <c r="G20">
-        <v>145892.626</v>
+        <v>145892.62599999999</v>
       </c>
       <c r="H20">
         <v>174145.266</v>
@@ -1318,59 +1336,57 @@
         <v>3413905202.776</v>
       </c>
       <c r="J20">
-        <v>3134723128.795</v>
+        <v>3134723128.7950001</v>
       </c>
       <c r="K20">
-        <v>3698762160.615</v>
+        <v>3698762160.6149998</v>
       </c>
       <c r="L20">
-        <v>21237111135.783</v>
+        <v>21237111135.783001</v>
       </c>
       <c r="M20">
-        <v>19405039461.573</v>
+        <v>19405039461.573002</v>
       </c>
       <c r="N20">
-        <v>23162717570.877</v>
-      </c>
-    </row>
-    <row r="21">
-      <c r="A21" t="inlineStr">
-        <is>
-          <t>All</t>
-        </is>
+        <v>23162717570.876999</v>
+      </c>
+    </row>
+    <row r="21" spans="1:14" x14ac:dyDescent="0.2">
+      <c r="A21" t="s">
+        <v>24</v>
       </c>
       <c r="C21">
-        <v>276112.127</v>
+        <v>276112.12699999998</v>
       </c>
       <c r="D21">
-        <v>254826.115</v>
+        <v>254826.11499999999</v>
       </c>
       <c r="E21">
-        <v>297736.8180000001</v>
+        <v>297736.81800000009</v>
       </c>
       <c r="F21">
-        <v>764403.532</v>
+        <v>764403.53200000001</v>
       </c>
       <c r="G21">
-        <v>716822.4040000002</v>
+        <v>716822.40400000021</v>
       </c>
       <c r="H21">
-        <v>812769.2289999999</v>
+        <v>812769.22899999993</v>
       </c>
       <c r="I21">
         <v>3413905202.776</v>
       </c>
       <c r="J21">
-        <v>3134723128.795</v>
+        <v>3134723128.7950001</v>
       </c>
       <c r="K21">
-        <v>3698762160.615</v>
+        <v>3698762160.6149998</v>
       </c>
       <c r="L21">
         <v>101670527022.612</v>
       </c>
       <c r="M21">
-        <v>95326932709.70702</v>
+        <v>95326932709.707016</v>
       </c>
       <c r="N21">
         <v>108130473702.172</v>

--- a/output/Tables/Best practice/Residence/HIA_area_2019_1000replicate_RES.xlsx
+++ b/output/Tables/Best practice/Residence/HIA_area_2019_1000replicate_RES.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/ines/Documents/PhD/PROJETS/MARCHE/HIA_walking_steps/output/Tables/Best practice/Residence/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{9C367C58-EC0C-3C4E-8AAD-54FF51AFE991}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{59AAA77C-7C30-134E-BC41-13CE61B79210}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="240" yWindow="500" windowWidth="26320" windowHeight="15140" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
